--- a/order_forms/033_tournament_participant_bib_printing_order_form--order_forms.xlsx
+++ b/order_forms/033_tournament_participant_bib_printing_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,8 +872,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -935,12 +935,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'color'}</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Color'}</t>
+          <t>Color</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'black_and_white'}</t>
+          <t>black_and_white</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Black and White'}</t>
+          <t>Black and White</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'full_color'}</t>
+          <t>full_color</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Full Color'}</t>
+          <t>Full Color</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'single_sided'}</t>
+          <t>single_sided</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Single Sided'}</t>
+          <t>Single Sided</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'double_sided'}</t>
+          <t>double_sided</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Double Sided'}</t>
+          <t>Double Sided</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'full_sided'}</t>
+          <t>full_sided</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Full Sided'}</t>
+          <t>Full Sided</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'top'}</t>
+          <t>top</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Top'}</t>
+          <t>Top</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'bottom'}</t>
+          <t>bottom</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Bottom'}</t>
+          <t>Bottom</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'center'}</t>
+          <t>center</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Center'}</t>
+          <t>Center</t>
         </is>
       </c>
     </row>
